--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P542"/>
+  <dimension ref="A1:P544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29694,6 +29694,114 @@
       <c r="P542" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>399.29</v>
+      </c>
+      <c r="C543" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="D543" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="E543" t="n">
+        <v>376.79</v>
+      </c>
+      <c r="F543" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="G543" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="H543" t="n">
+        <v>378.97</v>
+      </c>
+      <c r="I543" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="J543" t="n">
+        <v>378.53</v>
+      </c>
+      <c r="K543" t="n">
+        <v>384.78</v>
+      </c>
+      <c r="L543" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="M543" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="N543" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="O543" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>398.14</v>
+      </c>
+      <c r="C544" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="D544" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="E544" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="F544" t="n">
+        <v>381.69</v>
+      </c>
+      <c r="G544" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="H544" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="I544" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="J544" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="K544" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="L544" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="M544" t="n">
+        <v>381.64</v>
+      </c>
+      <c r="N544" t="n">
+        <v>373.04</v>
+      </c>
+      <c r="O544" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B550"/>
+  <dimension ref="A1:B552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35211,6 +35319,26 @@
       </c>
       <c r="B550" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -35379,28 +35507,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1204193422619945</v>
+        <v>-0.1136549340588477</v>
       </c>
       <c r="J2" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K2" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009236211264654903</v>
+        <v>0.00825997060884287</v>
       </c>
       <c r="M2" t="n">
-        <v>7.850800302229525</v>
+        <v>7.856101177652283</v>
       </c>
       <c r="N2" t="n">
-        <v>93.42303660855234</v>
+        <v>93.46742267332118</v>
       </c>
       <c r="O2" t="n">
-        <v>9.665559301383047</v>
+        <v>9.667855122689891</v>
       </c>
       <c r="P2" t="n">
-        <v>391.5810159014196</v>
+        <v>391.5131539969063</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35461,28 +35589,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5346461490743227</v>
+        <v>0.5395731000855315</v>
       </c>
       <c r="J3" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K3" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1281802218814514</v>
+        <v>0.1308495272511673</v>
       </c>
       <c r="M3" t="n">
-        <v>8.652641929023792</v>
+        <v>8.650435999755608</v>
       </c>
       <c r="N3" t="n">
-        <v>116.7679875041633</v>
+        <v>116.543412627195</v>
       </c>
       <c r="O3" t="n">
-        <v>10.80592372285513</v>
+        <v>10.79552743626707</v>
       </c>
       <c r="P3" t="n">
-        <v>352.4389620896831</v>
+        <v>352.3895317967951</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -35543,28 +35671,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7370141484933128</v>
+        <v>0.74039502225628</v>
       </c>
       <c r="J4" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K4" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1976975389817796</v>
+        <v>0.2001679522851553</v>
       </c>
       <c r="M4" t="n">
-        <v>8.965743456455845</v>
+        <v>8.948757891581069</v>
       </c>
       <c r="N4" t="n">
-        <v>132.3956519220996</v>
+        <v>132.0065781334236</v>
       </c>
       <c r="O4" t="n">
-        <v>11.50633094961637</v>
+        <v>11.48941156602128</v>
       </c>
       <c r="P4" t="n">
-        <v>353.9254633071502</v>
+        <v>353.8915472621153</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35621,28 +35749,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8355149712665781</v>
+        <v>0.8392612526399061</v>
       </c>
       <c r="J5" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K5" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L5" t="n">
-        <v>0.269034898237768</v>
+        <v>0.2719939816539442</v>
       </c>
       <c r="M5" t="n">
-        <v>8.415224615600847</v>
+        <v>8.401497208105971</v>
       </c>
       <c r="N5" t="n">
-        <v>113.9152080607469</v>
+        <v>113.6146561709539</v>
       </c>
       <c r="O5" t="n">
-        <v>10.67310676704524</v>
+        <v>10.65901759877307</v>
       </c>
       <c r="P5" t="n">
-        <v>349.3187392950603</v>
+        <v>349.2811536521617</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35699,28 +35827,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7898957309279667</v>
+        <v>0.7933829983093053</v>
       </c>
       <c r="J6" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K6" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2658191224330106</v>
+        <v>0.2687387030929935</v>
       </c>
       <c r="M6" t="n">
-        <v>8.134169860185645</v>
+        <v>8.119613961007659</v>
       </c>
       <c r="N6" t="n">
-        <v>103.5002962789789</v>
+        <v>103.222051986417</v>
       </c>
       <c r="O6" t="n">
-        <v>10.17350953599489</v>
+        <v>10.15982539153193</v>
       </c>
       <c r="P6" t="n">
-        <v>355.3996711897473</v>
+        <v>355.3646846348758</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35777,28 +35905,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6849486099372813</v>
+        <v>0.6900905212253025</v>
       </c>
       <c r="J7" t="n">
+        <v>543</v>
+      </c>
+      <c r="K7" t="n">
         <v>541</v>
       </c>
-      <c r="K7" t="n">
-        <v>539</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1971083102599462</v>
+        <v>0.2003124686677693</v>
       </c>
       <c r="M7" t="n">
-        <v>8.937664893195771</v>
+        <v>8.929413319116334</v>
       </c>
       <c r="N7" t="n">
-        <v>113.5976695227712</v>
+        <v>113.3992851727099</v>
       </c>
       <c r="O7" t="n">
-        <v>10.65822074845381</v>
+        <v>10.64891004623055</v>
       </c>
       <c r="P7" t="n">
-        <v>356.8261209976524</v>
+        <v>356.7740994331463</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35855,28 +35983,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5807142707218992</v>
+        <v>0.5862567138563023</v>
       </c>
       <c r="J8" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K8" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1898747528571203</v>
+        <v>0.1934489828481739</v>
       </c>
       <c r="M8" t="n">
-        <v>7.484174595416214</v>
+        <v>7.487724028083271</v>
       </c>
       <c r="N8" t="n">
-        <v>86.4161977357267</v>
+        <v>86.3585594191</v>
       </c>
       <c r="O8" t="n">
-        <v>9.29603128951956</v>
+        <v>9.292930615209608</v>
       </c>
       <c r="P8" t="n">
-        <v>355.6502540562856</v>
+        <v>355.5946477387851</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35933,28 +36061,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8306276210096984</v>
+        <v>0.8360924185113904</v>
       </c>
       <c r="J9" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K9" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3956377146199573</v>
+        <v>0.3995186168668927</v>
       </c>
       <c r="M9" t="n">
-        <v>6.14382247912664</v>
+        <v>6.153758926181501</v>
       </c>
       <c r="N9" t="n">
-        <v>63.29911215560232</v>
+        <v>63.31920222417034</v>
       </c>
       <c r="O9" t="n">
-        <v>7.956073915921239</v>
+        <v>7.957336377467673</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7609507679663</v>
+        <v>347.7061236674419</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36011,28 +36139,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6285307779835948</v>
+        <v>0.6346252016620064</v>
       </c>
       <c r="J10" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K10" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2815125041356132</v>
+        <v>0.2858232665878657</v>
       </c>
       <c r="M10" t="n">
-        <v>6.0852125643339</v>
+        <v>6.10245694775822</v>
       </c>
       <c r="N10" t="n">
-        <v>60.28054260663257</v>
+        <v>60.37065764871883</v>
       </c>
       <c r="O10" t="n">
-        <v>7.764054521101238</v>
+        <v>7.769855703210893</v>
       </c>
       <c r="P10" t="n">
-        <v>352.8883066518314</v>
+        <v>352.8269301854789</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36089,28 +36217,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.597747264973195</v>
+        <v>0.6058294002510478</v>
       </c>
       <c r="J11" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K11" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2344845812482774</v>
+        <v>0.2391993900279922</v>
       </c>
       <c r="M11" t="n">
-        <v>6.941548273584186</v>
+        <v>6.971041370883322</v>
       </c>
       <c r="N11" t="n">
-        <v>69.73926686877205</v>
+        <v>70.03169434905642</v>
       </c>
       <c r="O11" t="n">
-        <v>8.351003943764608</v>
+        <v>8.368494150625692</v>
       </c>
       <c r="P11" t="n">
-        <v>356.4825522801262</v>
+        <v>356.4011596263441</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36167,28 +36295,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8136528714942072</v>
+        <v>0.8210975020830256</v>
       </c>
       <c r="J12" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K12" t="n">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2225725436463256</v>
+        <v>0.2263866471469944</v>
       </c>
       <c r="M12" t="n">
-        <v>9.409216106171254</v>
+        <v>9.420011433842557</v>
       </c>
       <c r="N12" t="n">
-        <v>138.7663696273445</v>
+        <v>138.7213511984006</v>
       </c>
       <c r="O12" t="n">
-        <v>11.77991382087936</v>
+        <v>11.77800285270812</v>
       </c>
       <c r="P12" t="n">
-        <v>352.429542712162</v>
+        <v>352.3546363318125</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36245,28 +36373,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5316642340160397</v>
+        <v>0.5399362396054854</v>
       </c>
       <c r="J13" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K13" t="n">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08404615522066927</v>
+        <v>0.08676460824416898</v>
       </c>
       <c r="M13" t="n">
-        <v>9.523150111425592</v>
+        <v>9.539401050774391</v>
       </c>
       <c r="N13" t="n">
-        <v>184.8622558184981</v>
+        <v>184.759074266246</v>
       </c>
       <c r="O13" t="n">
-        <v>13.5964059890288</v>
+        <v>13.59261101724926</v>
       </c>
       <c r="P13" t="n">
-        <v>355.9902543048257</v>
+        <v>355.907024945036</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36323,28 +36451,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4308985901970698</v>
+        <v>0.4354736046168995</v>
       </c>
       <c r="J14" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K14" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06465639073055229</v>
+        <v>0.0663149565747474</v>
       </c>
       <c r="M14" t="n">
-        <v>9.673704600252959</v>
+        <v>9.66351343395387</v>
       </c>
       <c r="N14" t="n">
-        <v>160.9482915154248</v>
+        <v>160.5306238987968</v>
       </c>
       <c r="O14" t="n">
-        <v>12.68653977707968</v>
+        <v>12.67006803055125</v>
       </c>
       <c r="P14" t="n">
-        <v>355.3742226142263</v>
+        <v>355.3281684494586</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36401,28 +36529,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2357992065871547</v>
+        <v>0.2375146698230424</v>
       </c>
       <c r="J15" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K15" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02587734000145581</v>
+        <v>0.02642180986955023</v>
       </c>
       <c r="M15" t="n">
-        <v>8.367281257269944</v>
+        <v>8.347128133431141</v>
       </c>
       <c r="N15" t="n">
-        <v>125.7082856667715</v>
+        <v>125.2718491244765</v>
       </c>
       <c r="O15" t="n">
-        <v>11.21197064154074</v>
+        <v>11.1924907471249</v>
       </c>
       <c r="P15" t="n">
-        <v>359.4207706718875</v>
+        <v>359.4035627767146</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36460,7 +36588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P542"/>
+  <dimension ref="A1:P544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80847,6 +80975,170 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-40.78951322054809,172.21037495744966</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-40.788963540837834,172.21098060998332</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-40.78831209346247,172.21124780535837</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-40.78768632040673,172.21160041319422</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-40.78704731076224,172.21187025224637</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-40.78640715192712,172.21211392719923</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-40.78576231609258,172.21239021491255</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-40.78511041361572,172.21264661632526</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-40.78445293274386,172.2128772563644</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-40.783786949314056,172.2130453267218</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-40.78313236218575,172.2132462734743</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-40.78247559851569,172.21346412683414</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-40.78182999517278,172.21376508299494</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-40.78117682960449,172.2140224799082</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-40.78951703124905,172.2103876317032</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-40.78896251361992,172.21097719346577</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-40.78831669935228,172.21126312444596</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-40.7876844648091,172.2115942415267</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-40.78704650752696,172.2118672318343</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-40.786404526996755,172.21210221878954</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-40.78576012182395,172.21238006987238</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-40.78510851521737,172.21263783923592</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-40.78445199587787,172.21287292485408</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-40.78378815848141,172.21305128043488</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-40.78313399583671,172.2132552639203</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-40.78247936620036,172.2134858480993</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-40.78183260045563,172.2137801028832</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-40.78117951502326,172.21403796180385</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P544"/>
+  <dimension ref="A1:P549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29802,6 +29802,276 @@
       <c r="P544" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>389.09</v>
+      </c>
+      <c r="C545" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="D545" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="E545" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="F545" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="G545" t="n">
+        <v>380.53</v>
+      </c>
+      <c r="H545" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="I545" t="n">
+        <v>376.06</v>
+      </c>
+      <c r="J545" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="K545" t="n">
+        <v>382.01</v>
+      </c>
+      <c r="L545" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="M545" t="n">
+        <v>378.12</v>
+      </c>
+      <c r="N545" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="O545" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>381.95</v>
+      </c>
+      <c r="C546" t="n">
+        <v>369.39</v>
+      </c>
+      <c r="D546" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="E546" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="F546" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="G546" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="H546" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>376.12</v>
+      </c>
+      <c r="J546" t="n">
+        <v>378.46</v>
+      </c>
+      <c r="K546" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="L546" t="n">
+        <v>383.83</v>
+      </c>
+      <c r="M546" t="n">
+        <v>380.44</v>
+      </c>
+      <c r="N546" t="n">
+        <v>369.39</v>
+      </c>
+      <c r="O546" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="C547" t="n">
+        <v>370.27</v>
+      </c>
+      <c r="D547" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="E547" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="F547" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="G547" t="n">
+        <v>383.77</v>
+      </c>
+      <c r="H547" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="I547" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="J547" t="n">
+        <v>378.98</v>
+      </c>
+      <c r="K547" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="L547" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="M547" t="n">
+        <v>381.23</v>
+      </c>
+      <c r="N547" t="n">
+        <v>369.93</v>
+      </c>
+      <c r="O547" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="C548" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="D548" t="n">
+        <v>377.09</v>
+      </c>
+      <c r="E548" t="n">
+        <v>381.28</v>
+      </c>
+      <c r="F548" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="G548" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="H548" t="n">
+        <v>379.94</v>
+      </c>
+      <c r="I548" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="J548" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="K548" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="L548" t="n">
+        <v>384.33</v>
+      </c>
+      <c r="M548" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="N548" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="O548" t="n">
+        <v>364.61</v>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="C549" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="D549" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="E549" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="F549" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="G549" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="H549" t="n">
+        <v>380.65</v>
+      </c>
+      <c r="I549" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="J549" t="n">
+        <v>379.58</v>
+      </c>
+      <c r="K549" t="n">
+        <v>383.42</v>
+      </c>
+      <c r="L549" t="n">
+        <v>385.26</v>
+      </c>
+      <c r="M549" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="N549" t="n">
+        <v>369.72</v>
+      </c>
+      <c r="O549" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29816,7 +30086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B552"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35339,6 +35609,56 @@
       </c>
       <c r="B552" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>
@@ -35507,28 +35827,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1136549340588477</v>
+        <v>-0.1240451861672693</v>
       </c>
       <c r="J2" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K2" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00825997060884287</v>
+        <v>0.009942243325683497</v>
       </c>
       <c r="M2" t="n">
-        <v>7.856101177652283</v>
+        <v>7.850102727344742</v>
       </c>
       <c r="N2" t="n">
-        <v>93.46742267332118</v>
+        <v>93.12212656346472</v>
       </c>
       <c r="O2" t="n">
-        <v>9.667855122689891</v>
+        <v>9.649980650937323</v>
       </c>
       <c r="P2" t="n">
-        <v>391.5131539969063</v>
+        <v>391.617925512057</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35589,28 +35909,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5395731000855315</v>
+        <v>0.5464261290497491</v>
       </c>
       <c r="J3" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K3" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1308495272511673</v>
+        <v>0.1356248082773185</v>
       </c>
       <c r="M3" t="n">
-        <v>8.650435999755608</v>
+        <v>8.612261593544112</v>
       </c>
       <c r="N3" t="n">
-        <v>116.543412627195</v>
+        <v>115.6492937462229</v>
       </c>
       <c r="O3" t="n">
-        <v>10.79552743626707</v>
+        <v>10.75403616072695</v>
       </c>
       <c r="P3" t="n">
-        <v>352.3895317967951</v>
+        <v>352.3204710956766</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -35671,28 +35991,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.74039502225628</v>
+        <v>0.7450852904992583</v>
       </c>
       <c r="J4" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K4" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2001679522851553</v>
+        <v>0.204935733293761</v>
       </c>
       <c r="M4" t="n">
-        <v>8.948757891581069</v>
+        <v>8.888928259011113</v>
       </c>
       <c r="N4" t="n">
-        <v>132.0065781334236</v>
+        <v>130.8921001605117</v>
       </c>
       <c r="O4" t="n">
-        <v>11.48941156602128</v>
+        <v>11.44080854487617</v>
       </c>
       <c r="P4" t="n">
-        <v>353.8915472621153</v>
+        <v>353.8442611245442</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35749,28 +36069,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8392612526399061</v>
+        <v>0.8505991762118666</v>
       </c>
       <c r="J5" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K5" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2719939816539442</v>
+        <v>0.2800009828083967</v>
       </c>
       <c r="M5" t="n">
-        <v>8.401497208105971</v>
+        <v>8.377654512872864</v>
       </c>
       <c r="N5" t="n">
-        <v>113.6146561709539</v>
+        <v>113.0678607197187</v>
       </c>
       <c r="O5" t="n">
-        <v>10.65901759877307</v>
+        <v>10.63333723342389</v>
       </c>
       <c r="P5" t="n">
-        <v>349.2811536521617</v>
+        <v>349.1668588377547</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35827,28 +36147,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7933829983093053</v>
+        <v>0.802545356058316</v>
       </c>
       <c r="J6" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K6" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2687387030929935</v>
+        <v>0.2761539287934346</v>
       </c>
       <c r="M6" t="n">
-        <v>8.119613961007659</v>
+        <v>8.085243386943404</v>
       </c>
       <c r="N6" t="n">
-        <v>103.222051986417</v>
+        <v>102.6008784629619</v>
       </c>
       <c r="O6" t="n">
-        <v>10.15982539153193</v>
+        <v>10.12920917263346</v>
       </c>
       <c r="P6" t="n">
-        <v>355.3646846348758</v>
+        <v>355.2723204357856</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35905,28 +36225,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6900905212253025</v>
+        <v>0.7029241846777927</v>
       </c>
       <c r="J7" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K7" t="n">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2003124686677693</v>
+        <v>0.2083448890212928</v>
       </c>
       <c r="M7" t="n">
-        <v>8.929413319116334</v>
+        <v>8.909004763425738</v>
       </c>
       <c r="N7" t="n">
-        <v>113.3992851727099</v>
+        <v>112.9332151747738</v>
       </c>
       <c r="O7" t="n">
-        <v>10.64891004623055</v>
+        <v>10.6270040545195</v>
       </c>
       <c r="P7" t="n">
-        <v>356.7740994331463</v>
+        <v>356.6436700856731</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35983,28 +36303,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5862567138563023</v>
+        <v>0.598258749220186</v>
       </c>
       <c r="J8" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K8" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1934489828481739</v>
+        <v>0.2017081165530675</v>
       </c>
       <c r="M8" t="n">
-        <v>7.487724028083271</v>
+        <v>7.485795766343336</v>
       </c>
       <c r="N8" t="n">
-        <v>86.3585594191</v>
+        <v>86.08616648254167</v>
       </c>
       <c r="O8" t="n">
-        <v>9.292930615209608</v>
+        <v>9.278263117768415</v>
       </c>
       <c r="P8" t="n">
-        <v>355.5946477387851</v>
+        <v>355.4736740314343</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36061,28 +36381,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8360924185113904</v>
+        <v>0.8475608565169076</v>
       </c>
       <c r="J9" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K9" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3995186168668927</v>
+        <v>0.4085613194141229</v>
       </c>
       <c r="M9" t="n">
-        <v>6.153758926181501</v>
+        <v>6.16514385727638</v>
       </c>
       <c r="N9" t="n">
-        <v>63.31920222417034</v>
+        <v>63.19914038192108</v>
       </c>
       <c r="O9" t="n">
-        <v>7.957336377467673</v>
+        <v>7.949788700457458</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7061236674419</v>
+        <v>347.5905401047011</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36139,28 +36459,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6346252016620064</v>
+        <v>0.6493369572669525</v>
       </c>
       <c r="J10" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K10" t="n">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2858232665878657</v>
+        <v>0.2963560677241807</v>
       </c>
       <c r="M10" t="n">
-        <v>6.10245694775822</v>
+        <v>6.141319951432683</v>
       </c>
       <c r="N10" t="n">
-        <v>60.37065764871883</v>
+        <v>60.56459681643838</v>
       </c>
       <c r="O10" t="n">
-        <v>7.769855703210893</v>
+        <v>7.782325925868075</v>
       </c>
       <c r="P10" t="n">
-        <v>352.8269301854789</v>
+        <v>352.6780982629351</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36217,28 +36537,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6058294002510478</v>
+        <v>0.6229502699589475</v>
       </c>
       <c r="J11" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K11" t="n">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2391993900279922</v>
+        <v>0.2501034552314029</v>
       </c>
       <c r="M11" t="n">
-        <v>6.971041370883322</v>
+        <v>7.022665115824185</v>
       </c>
       <c r="N11" t="n">
-        <v>70.03169434905642</v>
+        <v>70.39274182469465</v>
       </c>
       <c r="O11" t="n">
-        <v>8.368494150625692</v>
+        <v>8.390038249298668</v>
       </c>
       <c r="P11" t="n">
-        <v>356.4011596263441</v>
+        <v>356.2279665362187</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36295,28 +36615,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8210975020830256</v>
+        <v>0.8370098418612881</v>
       </c>
       <c r="J12" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K12" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2263866471469944</v>
+        <v>0.2351848182074365</v>
       </c>
       <c r="M12" t="n">
-        <v>9.420011433842557</v>
+        <v>9.430183455393834</v>
       </c>
       <c r="N12" t="n">
-        <v>138.7213511984006</v>
+        <v>138.3254101408811</v>
       </c>
       <c r="O12" t="n">
-        <v>11.77800285270812</v>
+        <v>11.76118234451286</v>
       </c>
       <c r="P12" t="n">
-        <v>352.3546363318125</v>
+        <v>352.1937914978503</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36373,28 +36693,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5399362396054854</v>
+        <v>0.5559012501176108</v>
       </c>
       <c r="J13" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K13" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08676460824416898</v>
+        <v>0.09255905823843402</v>
       </c>
       <c r="M13" t="n">
-        <v>9.539401050774391</v>
+        <v>9.550647348619828</v>
       </c>
       <c r="N13" t="n">
-        <v>184.759074266246</v>
+        <v>183.9451598122483</v>
       </c>
       <c r="O13" t="n">
-        <v>13.59261101724926</v>
+        <v>13.5626383794691</v>
       </c>
       <c r="P13" t="n">
-        <v>355.907024945036</v>
+        <v>355.7456547999957</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36451,28 +36771,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4354736046168995</v>
+        <v>0.4400481053749122</v>
       </c>
       <c r="J14" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K14" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0663149565747474</v>
+        <v>0.06870758234075269</v>
       </c>
       <c r="M14" t="n">
-        <v>9.66351343395387</v>
+        <v>9.600720189407696</v>
       </c>
       <c r="N14" t="n">
-        <v>160.5306238987968</v>
+        <v>159.1307560058118</v>
       </c>
       <c r="O14" t="n">
-        <v>12.67006803055125</v>
+        <v>12.6147039602922</v>
       </c>
       <c r="P14" t="n">
-        <v>355.3281684494586</v>
+        <v>355.2819074449628</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36529,28 +36849,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2375146698230424</v>
+        <v>0.2339496646281206</v>
       </c>
       <c r="J15" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="K15" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02642180986955023</v>
+        <v>0.02608728935230931</v>
       </c>
       <c r="M15" t="n">
-        <v>8.347128133431141</v>
+        <v>8.288526326073676</v>
       </c>
       <c r="N15" t="n">
-        <v>125.2718491244765</v>
+        <v>124.1803399337719</v>
       </c>
       <c r="O15" t="n">
-        <v>11.1924907471249</v>
+        <v>11.14362328570792</v>
       </c>
       <c r="P15" t="n">
-        <v>359.4035627767146</v>
+        <v>359.4394720460143</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36588,7 +36908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P544"/>
+  <dimension ref="A1:P549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81139,6 +81459,416 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-40.789547019760526,172.2104873726196</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-40.78896990295947,172.21100177035248</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-40.78832876080958,172.21130324062798</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-40.78769082685678,172.2116154015311</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-40.7870537663911,172.21189452741265</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-40.786411280455965,172.21213234236976</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-40.78576825787175,172.21241768631683</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-40.78511425971944,172.21266439848188</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-40.784456828132306,172.21289526632964</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-40.78379339045198,172.2130770416958</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-40.78314013249367,172.21328903572794</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-40.78248642057771,172.2135265177089</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>-40.781840416292496,172.21382516255514</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>-40.78119059736391,172.21410185352104</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-40.789570679144575,172.2105660633073</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-40.788978485190384,172.21103031481528</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-40.78832332652832,172.2112851663024</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-40.78768595591436,172.21159920090236</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-40.78704882798422,172.21187595746935</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-40.786406336414906,172.21211028963495</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-40.7857669265193,172.212411530898</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-40.78511411179244,172.21266371455272</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-40.784453105324424,172.2128780542742</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-40.783791437183645,172.2130674241579</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-40.78313604837152,172.21326655960954</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-40.78248177110334,172.21349971273796</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>-40.78183991527783,172.2138222741143</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>-40.78118895405342,172.21409237952182</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-40.789569320553944,172.21056154465285</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-40.78897556922083,172.2110206163097</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-40.78831941649498,172.21127216160656</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-40.78768294056794,172.21158917194293</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-40.787046537276424,172.21186734370144</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-40.78640302339534,172.21209551203103</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-40.78576330228045,172.21239477448134</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-40.78511312561223,172.21265915502522</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-40.784451823297275,172.21287212694432</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-40.78379020476391,172.21306135594978</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-40.78313489643885,172.21326022019204</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-40.782480187875734,172.21349058518405</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>-40.78183883308593,172.21381603508226</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>-40.78118769150946,172.21408510071785</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-40.789581050818555,172.2106005593829</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-40.78897149348929,172.2110070604454</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-40.78831915140792,172.21127127993233</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-40.787671442480715,172.21155092965543</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-40.787039099909,172.21183937692655</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-40.786403150819204,172.21209608040036</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-40.78575992458627,172.21237915795868</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-40.78510935347128,172.21264171483375</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-40.784450146799784,172.21286437582097</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-40.783789948978644,172.2130600965104</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-40.78313500116001,172.21326079650268</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-40.7824829735542,172.21350664505766</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-40.781838211827456,172.21381245341578</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>-40.781185487066544,172.21407239169577</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-40.789583536042436,172.21060882521735</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-40.78897149348929,172.2110070604454</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-40.788316533672834,172.2112625733996</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-40.787671575023595,172.21155137048865</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-40.78703895116159,172.21183881759112</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-40.786401927549996,172.21209062405467</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-40.785758174101595,172.21237106472495</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-40.785109402780314,172.21264194281008</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>-40.78445034403481,172.21286528771782</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>-40.783790111751095,172.21306089797181</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-40.78313305334584,172.21325007712448</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-40.78248110975519,172.2134958999622</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>-40.78183925393838,172.21381846137245</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>-40.78118608827838,172.21407585779264</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P549"/>
+  <dimension ref="A1:P551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30070,6 +30070,114 @@
         <v>364.31</v>
       </c>
       <c r="P549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>372.14</v>
+      </c>
+      <c r="C550" t="n">
+        <v>367.69</v>
+      </c>
+      <c r="D550" t="n">
+        <v>376.74</v>
+      </c>
+      <c r="E550" t="n">
+        <v>382.04</v>
+      </c>
+      <c r="F550" t="n">
+        <v>383.79</v>
+      </c>
+      <c r="G550" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="H550" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="I550" t="n">
+        <v>376</v>
+      </c>
+      <c r="J550" t="n">
+        <v>378.29</v>
+      </c>
+      <c r="K550" t="n">
+        <v>381.33</v>
+      </c>
+      <c r="L550" t="n">
+        <v>383.19</v>
+      </c>
+      <c r="M550" t="n">
+        <v>377.93</v>
+      </c>
+      <c r="N550" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="O550" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="C551" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="D551" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="E551" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="F551" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="G551" t="n">
+        <v>386.22</v>
+      </c>
+      <c r="H551" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>378.42</v>
+      </c>
+      <c r="J551" t="n">
+        <v>379.38</v>
+      </c>
+      <c r="K551" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="L551" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="M551" t="n">
+        <v>378.72</v>
+      </c>
+      <c r="N551" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="O551" t="n">
+        <v>363.49</v>
+      </c>
+      <c r="P551" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30086,7 +30194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B557"/>
+  <dimension ref="A1:B559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35659,6 +35767,26 @@
       </c>
       <c r="B557" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -35827,28 +35955,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1240451861672693</v>
+        <v>-0.134462048193156</v>
       </c>
       <c r="J2" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K2" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009942243325683497</v>
+        <v>0.01162549233636434</v>
       </c>
       <c r="M2" t="n">
-        <v>7.850102727344742</v>
+        <v>7.884735235586777</v>
       </c>
       <c r="N2" t="n">
-        <v>93.12212656346472</v>
+        <v>93.72887860889729</v>
       </c>
       <c r="O2" t="n">
-        <v>9.649980650937323</v>
+        <v>9.681367600132601</v>
       </c>
       <c r="P2" t="n">
-        <v>391.617925512057</v>
+        <v>391.7233996190591</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35909,28 +36037,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5464261290497491</v>
+        <v>0.5479839268664144</v>
       </c>
       <c r="J3" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K3" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1356248082773185</v>
+        <v>0.1370860778072746</v>
       </c>
       <c r="M3" t="n">
-        <v>8.612261593544112</v>
+        <v>8.590116662519554</v>
       </c>
       <c r="N3" t="n">
-        <v>115.6492937462229</v>
+        <v>115.258658494801</v>
       </c>
       <c r="O3" t="n">
-        <v>10.75403616072695</v>
+        <v>10.73585853552481</v>
       </c>
       <c r="P3" t="n">
-        <v>352.3204710956766</v>
+        <v>352.3046921566677</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -35991,28 +36119,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7450852904992583</v>
+        <v>0.7472756602880539</v>
       </c>
       <c r="J4" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K4" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0.204935733293761</v>
+        <v>0.2069836835441465</v>
       </c>
       <c r="M4" t="n">
-        <v>8.888928259011113</v>
+        <v>8.866665031428061</v>
       </c>
       <c r="N4" t="n">
-        <v>130.8921001605117</v>
+        <v>130.4582296061858</v>
       </c>
       <c r="O4" t="n">
-        <v>11.44080854487617</v>
+        <v>11.42183127200651</v>
       </c>
       <c r="P4" t="n">
-        <v>353.8442611245442</v>
+        <v>353.8220818649947</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36069,28 +36197,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8505991762118666</v>
+        <v>0.8575681193618072</v>
       </c>
       <c r="J5" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K5" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2800009828083967</v>
+        <v>0.283956230625915</v>
       </c>
       <c r="M5" t="n">
-        <v>8.377654512872864</v>
+        <v>8.379817179719758</v>
       </c>
       <c r="N5" t="n">
-        <v>113.0678607197187</v>
+        <v>113.0808899204181</v>
       </c>
       <c r="O5" t="n">
-        <v>10.63333723342389</v>
+        <v>10.63394987389061</v>
       </c>
       <c r="P5" t="n">
-        <v>349.1668588377547</v>
+        <v>349.0962940595692</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36147,28 +36275,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.802545356058316</v>
+        <v>0.8077776842586919</v>
       </c>
       <c r="J6" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K6" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2761539287934346</v>
+        <v>0.2796881261404268</v>
       </c>
       <c r="M6" t="n">
-        <v>8.085243386943404</v>
+        <v>8.078416009613267</v>
       </c>
       <c r="N6" t="n">
-        <v>102.6008784629619</v>
+        <v>102.4693643138909</v>
       </c>
       <c r="O6" t="n">
-        <v>10.12920917263346</v>
+        <v>10.12271526389491</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2723204357856</v>
+        <v>355.2193380471418</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36225,28 +36353,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7029241846777927</v>
+        <v>0.7093391325784312</v>
       </c>
       <c r="J7" t="n">
+        <v>550</v>
+      </c>
+      <c r="K7" t="n">
         <v>548</v>
       </c>
-      <c r="K7" t="n">
-        <v>546</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2083448890212928</v>
+        <v>0.2119967995750255</v>
       </c>
       <c r="M7" t="n">
-        <v>8.909004763425738</v>
+        <v>8.906975490055592</v>
       </c>
       <c r="N7" t="n">
-        <v>112.9332151747738</v>
+        <v>112.8782267403587</v>
       </c>
       <c r="O7" t="n">
-        <v>10.6270040545195</v>
+        <v>10.62441653646725</v>
       </c>
       <c r="P7" t="n">
-        <v>356.6436700856731</v>
+        <v>356.5781723532882</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36303,28 +36431,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.598258749220186</v>
+        <v>0.6029645376590219</v>
       </c>
       <c r="J8" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K8" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2017081165530675</v>
+        <v>0.2049991332768099</v>
       </c>
       <c r="M8" t="n">
-        <v>7.485795766343336</v>
+        <v>7.484536308924212</v>
       </c>
       <c r="N8" t="n">
-        <v>86.08616648254167</v>
+        <v>85.97316469201611</v>
       </c>
       <c r="O8" t="n">
-        <v>9.278263117768415</v>
+        <v>9.27217151976904</v>
       </c>
       <c r="P8" t="n">
-        <v>355.4736740314343</v>
+        <v>355.426021249824</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36381,28 +36509,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8475608565169076</v>
+        <v>0.8521314130177067</v>
       </c>
       <c r="J9" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K9" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4085613194141229</v>
+        <v>0.4121333207578292</v>
       </c>
       <c r="M9" t="n">
-        <v>6.16514385727638</v>
+        <v>6.169766743376147</v>
       </c>
       <c r="N9" t="n">
-        <v>63.19914038192108</v>
+        <v>63.15650116049171</v>
       </c>
       <c r="O9" t="n">
-        <v>7.949788700457458</v>
+        <v>7.947106464650623</v>
       </c>
       <c r="P9" t="n">
-        <v>347.5905401047011</v>
+        <v>347.5442573481035</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36459,28 +36587,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6493369572669525</v>
+        <v>0.6550856745766568</v>
       </c>
       <c r="J10" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K10" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2963560677241807</v>
+        <v>0.3005151482923607</v>
       </c>
       <c r="M10" t="n">
-        <v>6.141319951432683</v>
+        <v>6.156120171793749</v>
       </c>
       <c r="N10" t="n">
-        <v>60.56459681643838</v>
+        <v>60.63117636360239</v>
       </c>
       <c r="O10" t="n">
-        <v>7.782325925868075</v>
+        <v>7.786602363264891</v>
       </c>
       <c r="P10" t="n">
-        <v>352.6780982629351</v>
+        <v>352.6196683676398</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36537,28 +36665,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6229502699589475</v>
+        <v>0.6286262062766963</v>
       </c>
       <c r="J11" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K11" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2501034552314029</v>
+        <v>0.2540915349056019</v>
       </c>
       <c r="M11" t="n">
-        <v>7.022665115824185</v>
+        <v>7.035085797524411</v>
       </c>
       <c r="N11" t="n">
-        <v>70.39274182469465</v>
+        <v>70.41548061640863</v>
       </c>
       <c r="O11" t="n">
-        <v>8.390038249298668</v>
+        <v>8.391393246440582</v>
       </c>
       <c r="P11" t="n">
-        <v>356.2279665362187</v>
+        <v>356.1702774945817</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36615,28 +36743,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8370098418612881</v>
+        <v>0.8429629787527185</v>
       </c>
       <c r="J12" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K12" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2351848182074365</v>
+        <v>0.2386006596903792</v>
       </c>
       <c r="M12" t="n">
-        <v>9.430183455393834</v>
+        <v>9.431464125148777</v>
       </c>
       <c r="N12" t="n">
-        <v>138.3254101408811</v>
+        <v>138.1283103887154</v>
       </c>
       <c r="O12" t="n">
-        <v>11.76118234451286</v>
+        <v>11.75280010843014</v>
       </c>
       <c r="P12" t="n">
-        <v>352.1937914978503</v>
+        <v>352.1333320581873</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36693,28 +36821,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5559012501176108</v>
+        <v>0.5609419304085137</v>
       </c>
       <c r="J13" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K13" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09255905823843402</v>
+        <v>0.09457825315049839</v>
       </c>
       <c r="M13" t="n">
-        <v>9.550647348619828</v>
+        <v>9.546538112321887</v>
       </c>
       <c r="N13" t="n">
-        <v>183.9451598122483</v>
+        <v>183.4933300827809</v>
       </c>
       <c r="O13" t="n">
-        <v>13.5626383794691</v>
+        <v>13.54597099076994</v>
       </c>
       <c r="P13" t="n">
-        <v>355.7456547999957</v>
+        <v>355.6944621679338</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36771,28 +36899,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4400481053749122</v>
+        <v>0.4395207304659524</v>
       </c>
       <c r="J14" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K14" t="n">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06870758234075269</v>
+        <v>0.06899787237629662</v>
       </c>
       <c r="M14" t="n">
-        <v>9.600720189407696</v>
+        <v>9.569771823722061</v>
       </c>
       <c r="N14" t="n">
-        <v>159.1307560058118</v>
+        <v>158.5561003635143</v>
       </c>
       <c r="O14" t="n">
-        <v>12.6147039602922</v>
+        <v>12.59190614496131</v>
       </c>
       <c r="P14" t="n">
-        <v>355.2819074449628</v>
+        <v>355.2872615048527</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36849,28 +36977,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2339496646281206</v>
+        <v>0.2315067067927445</v>
       </c>
       <c r="J15" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K15" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02608728935230931</v>
+        <v>0.02572094617853682</v>
       </c>
       <c r="M15" t="n">
-        <v>8.288526326073676</v>
+        <v>8.270253259413295</v>
       </c>
       <c r="N15" t="n">
-        <v>124.1803399337719</v>
+        <v>123.79051633194</v>
       </c>
       <c r="O15" t="n">
-        <v>11.14362328570792</v>
+        <v>11.12611865530563</v>
       </c>
       <c r="P15" t="n">
-        <v>359.4394720460143</v>
+        <v>359.4642017258873</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36908,7 +37036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P549"/>
+  <dimension ref="A1:P551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81869,6 +81997,170 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-40.78960318585852,172.21067418043688</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-40.78898411831111,172.2110490505671</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-40.78832031116376,172.21127513725716</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-40.787668924166,172.2115425538248</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-40.78704026013876,172.21184373974302</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-40.786401927549996,172.21209062405467</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-40.785766507389766,172.21240959308102</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-40.78511440764647,172.21266508241104</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-40.78445352444863,172.21287999205518</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-40.783794971668634,172.21308482732215</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-40.78313738880184,172.21327393638654</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-40.78248680135337,172.21352871294374</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>-40.78184869304424,172.21387287960414</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>-40.78119430482988,172.21412322778937</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-40.789603384676035,172.21067484170408</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-40.78897374673944,172.21101455474417</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-40.7883183230108,172.2112685247004</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-40.78766521296425,172.21153021049665</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-40.78703469698432,172.2118228205988</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-40.7863967796226,172.21206766193538</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-40.7857595301109,172.21237733413133</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-40.78510844125378,172.2126374972714</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-40.78445083712235,172.21286756745994</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-40.78379385551576,172.21307933158587</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-40.78313544098888,172.21326321700755</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-40.78248521812805,172.21351958538847</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>-40.78184410375816,172.21384642148104</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>-40.78118773159022,172.214085331791</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P551"/>
+  <dimension ref="A1:P555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30178,6 +30178,222 @@
         <v>363.49</v>
       </c>
       <c r="P551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>372.34</v>
+      </c>
+      <c r="C552" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="D552" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="E552" t="n">
+        <v>384.25</v>
+      </c>
+      <c r="F552" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="G552" t="n">
+        <v>387.81</v>
+      </c>
+      <c r="H552" t="n">
+        <v>382.48</v>
+      </c>
+      <c r="I552" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="J552" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="K552" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="L552" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="M552" t="n">
+        <v>380.64</v>
+      </c>
+      <c r="N552" t="n">
+        <v>372.65</v>
+      </c>
+      <c r="O552" t="n">
+        <v>366.37</v>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="C553" t="n">
+        <v>372.58</v>
+      </c>
+      <c r="D553" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="E553" t="n">
+        <v>385.17</v>
+      </c>
+      <c r="F553" t="n">
+        <v>388.08</v>
+      </c>
+      <c r="G553" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="H553" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="I553" t="n">
+        <v>381.56</v>
+      </c>
+      <c r="J553" t="n">
+        <v>382.66</v>
+      </c>
+      <c r="K553" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="L553" t="n">
+        <v>385.07</v>
+      </c>
+      <c r="M553" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="N553" t="n">
+        <v>375.01</v>
+      </c>
+      <c r="O553" t="n">
+        <v>369.01</v>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="C554" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="D554" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="E554" t="n">
+        <v>384.62</v>
+      </c>
+      <c r="F554" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="G554" t="n">
+        <v>390.21</v>
+      </c>
+      <c r="H554" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="I554" t="n">
+        <v>381.58</v>
+      </c>
+      <c r="J554" t="n">
+        <v>382.44</v>
+      </c>
+      <c r="K554" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="L554" t="n">
+        <v>384.96</v>
+      </c>
+      <c r="M554" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="N554" t="n">
+        <v>375.28</v>
+      </c>
+      <c r="O554" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="C555" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D555" t="n">
+        <v>380.11</v>
+      </c>
+      <c r="E555" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="F555" t="n">
+        <v>388.54</v>
+      </c>
+      <c r="G555" t="n">
+        <v>390.6</v>
+      </c>
+      <c r="H555" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="I555" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="J555" t="n">
+        <v>383.04</v>
+      </c>
+      <c r="K555" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="L555" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="M555" t="n">
+        <v>382.72</v>
+      </c>
+      <c r="N555" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="O555" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="P555" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30194,7 +30410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35787,6 +36003,46 @@
       </c>
       <c r="B559" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>
@@ -35955,28 +36211,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.134462048193156</v>
+        <v>-0.151311434544089</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01162549233636434</v>
+        <v>0.0146802418652765</v>
       </c>
       <c r="M2" t="n">
-        <v>7.884735235586777</v>
+        <v>7.929601320138639</v>
       </c>
       <c r="N2" t="n">
-        <v>93.72887860889729</v>
+        <v>94.3243350533846</v>
       </c>
       <c r="O2" t="n">
-        <v>9.681367600132601</v>
+        <v>9.712071614922564</v>
       </c>
       <c r="P2" t="n">
-        <v>391.7233996190591</v>
+        <v>391.8946768579619</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36037,28 +36293,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5479839268664144</v>
+        <v>0.555008828900721</v>
       </c>
       <c r="J3" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1370860778072746</v>
+        <v>0.1415750310319698</v>
       </c>
       <c r="M3" t="n">
-        <v>8.590116662519554</v>
+        <v>8.568863059710585</v>
       </c>
       <c r="N3" t="n">
-        <v>115.258658494801</v>
+        <v>114.6441064478637</v>
       </c>
       <c r="O3" t="n">
-        <v>10.73585853552481</v>
+        <v>10.7071988142494</v>
       </c>
       <c r="P3" t="n">
-        <v>352.3046921566677</v>
+        <v>352.2332614026755</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36119,28 +36375,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7472756602880539</v>
+        <v>0.7546963224105661</v>
       </c>
       <c r="J4" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2069836835441465</v>
+        <v>0.2122390647804728</v>
       </c>
       <c r="M4" t="n">
-        <v>8.866665031428061</v>
+        <v>8.836316198919818</v>
       </c>
       <c r="N4" t="n">
-        <v>130.4582296061858</v>
+        <v>129.7626956290239</v>
       </c>
       <c r="O4" t="n">
-        <v>11.42183127200651</v>
+        <v>11.39134301252596</v>
       </c>
       <c r="P4" t="n">
-        <v>353.8220818649947</v>
+        <v>353.7466176614149</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36197,28 +36453,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8575681193618072</v>
+        <v>0.8737269265075616</v>
       </c>
       <c r="J5" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.283956230625915</v>
+        <v>0.2923684197090137</v>
       </c>
       <c r="M5" t="n">
-        <v>8.379817179719758</v>
+        <v>8.394036473589559</v>
       </c>
       <c r="N5" t="n">
-        <v>113.0808899204181</v>
+        <v>113.4134235011124</v>
       </c>
       <c r="O5" t="n">
-        <v>10.63394987389061</v>
+        <v>10.64957386476625</v>
       </c>
       <c r="P5" t="n">
-        <v>349.0962940595692</v>
+        <v>348.931998595934</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36275,28 +36531,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8077776842586919</v>
+        <v>0.8218813101043715</v>
       </c>
       <c r="J6" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K6" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2796881261404268</v>
+        <v>0.2877951379044503</v>
       </c>
       <c r="M6" t="n">
-        <v>8.078416009613267</v>
+        <v>8.080337057196125</v>
       </c>
       <c r="N6" t="n">
-        <v>102.4693643138909</v>
+        <v>102.6067578035359</v>
       </c>
       <c r="O6" t="n">
-        <v>10.12271526389491</v>
+        <v>10.12949938563283</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2193380471418</v>
+        <v>355.075928465434</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36353,28 +36609,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7093391325784312</v>
+        <v>0.7275415021911693</v>
       </c>
       <c r="J7" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K7" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2119967995750255</v>
+        <v>0.2207746640080345</v>
       </c>
       <c r="M7" t="n">
-        <v>8.906975490055592</v>
+        <v>8.92841569077815</v>
       </c>
       <c r="N7" t="n">
-        <v>112.8782267403587</v>
+        <v>113.505251465844</v>
       </c>
       <c r="O7" t="n">
-        <v>10.62441653646725</v>
+        <v>10.65388433698451</v>
       </c>
       <c r="P7" t="n">
-        <v>356.5781723532882</v>
+        <v>356.3915459523571</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36431,28 +36687,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6029645376590219</v>
+        <v>0.620369621453235</v>
       </c>
       <c r="J8" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K8" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2049991332768099</v>
+        <v>0.214122995399778</v>
       </c>
       <c r="M8" t="n">
-        <v>7.484536308924212</v>
+        <v>7.527254037028058</v>
       </c>
       <c r="N8" t="n">
-        <v>85.97316469201611</v>
+        <v>86.70189525258813</v>
       </c>
       <c r="O8" t="n">
-        <v>9.27217151976904</v>
+        <v>9.311385248854659</v>
       </c>
       <c r="P8" t="n">
-        <v>355.426021249824</v>
+        <v>355.2490251569812</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36509,28 +36765,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8521314130177067</v>
+        <v>0.8660136333546711</v>
       </c>
       <c r="J9" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K9" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4121333207578292</v>
+        <v>0.4200729180161195</v>
       </c>
       <c r="M9" t="n">
-        <v>6.169766743376147</v>
+        <v>6.209452517529593</v>
       </c>
       <c r="N9" t="n">
-        <v>63.15650116049171</v>
+        <v>63.55276334682964</v>
       </c>
       <c r="O9" t="n">
-        <v>7.947106464650623</v>
+        <v>7.971998704642998</v>
       </c>
       <c r="P9" t="n">
-        <v>347.5442573481035</v>
+        <v>347.4030946997963</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36587,28 +36843,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6550856745766568</v>
+        <v>0.670456270475038</v>
       </c>
       <c r="J10" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K10" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3005151482923607</v>
+        <v>0.3096618493690457</v>
       </c>
       <c r="M10" t="n">
-        <v>6.156120171793749</v>
+        <v>6.210058190344669</v>
       </c>
       <c r="N10" t="n">
-        <v>60.63117636360239</v>
+        <v>61.23199687696233</v>
       </c>
       <c r="O10" t="n">
-        <v>7.786602363264891</v>
+        <v>7.825087659378797</v>
       </c>
       <c r="P10" t="n">
-        <v>352.6196683676398</v>
+        <v>352.4627807844812</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36665,28 +36921,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6286262062766963</v>
+        <v>0.6423751993123155</v>
       </c>
       <c r="J11" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K11" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2540915349056019</v>
+        <v>0.2627843497654964</v>
       </c>
       <c r="M11" t="n">
-        <v>7.035085797524411</v>
+        <v>7.075139677930507</v>
       </c>
       <c r="N11" t="n">
-        <v>70.41548061640863</v>
+        <v>70.73525400402451</v>
       </c>
       <c r="O11" t="n">
-        <v>8.391393246440582</v>
+        <v>8.410425316476243</v>
       </c>
       <c r="P11" t="n">
-        <v>356.1702774945817</v>
+        <v>356.0299468596217</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36743,28 +36999,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8429629787527185</v>
+        <v>0.8562159206889137</v>
       </c>
       <c r="J12" t="n">
+        <v>554</v>
+      </c>
+      <c r="K12" t="n">
         <v>550</v>
       </c>
-      <c r="K12" t="n">
-        <v>546</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2386006596903792</v>
+        <v>0.2458357410144756</v>
       </c>
       <c r="M12" t="n">
-        <v>9.431464125148777</v>
+        <v>9.441641756278527</v>
       </c>
       <c r="N12" t="n">
-        <v>138.1283103887154</v>
+        <v>137.8966942768377</v>
       </c>
       <c r="O12" t="n">
-        <v>11.75280010843014</v>
+        <v>11.74294231770035</v>
       </c>
       <c r="P12" t="n">
-        <v>352.1333320581873</v>
+        <v>351.9981732681795</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36821,28 +37077,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5609419304085137</v>
+        <v>0.5751240289939457</v>
       </c>
       <c r="J13" t="n">
+        <v>554</v>
+      </c>
+      <c r="K13" t="n">
         <v>550</v>
       </c>
-      <c r="K13" t="n">
-        <v>546</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09457825315049839</v>
+        <v>0.09974513136167817</v>
       </c>
       <c r="M13" t="n">
-        <v>9.546538112321887</v>
+        <v>9.562730327822774</v>
       </c>
       <c r="N13" t="n">
-        <v>183.4933300827809</v>
+        <v>183.0472177648042</v>
       </c>
       <c r="O13" t="n">
-        <v>13.54597099076994</v>
+        <v>13.52949436471312</v>
       </c>
       <c r="P13" t="n">
-        <v>355.6944621679338</v>
+        <v>355.5498163827299</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36899,28 +37155,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4395207304659524</v>
+        <v>0.4493333988356901</v>
       </c>
       <c r="J14" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K14" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06899787237629662</v>
+        <v>0.07263386616064171</v>
       </c>
       <c r="M14" t="n">
-        <v>9.569771823722061</v>
+        <v>9.555298988065291</v>
       </c>
       <c r="N14" t="n">
-        <v>158.5561003635143</v>
+        <v>157.8379262572626</v>
       </c>
       <c r="O14" t="n">
-        <v>12.59190614496131</v>
+        <v>12.56335648850508</v>
       </c>
       <c r="P14" t="n">
-        <v>355.2872615048527</v>
+        <v>355.1871208613578</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36977,28 +37233,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2315067067927445</v>
+        <v>0.2344684612811009</v>
       </c>
       <c r="J15" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K15" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02572094617853682</v>
+        <v>0.02671433308730775</v>
       </c>
       <c r="M15" t="n">
-        <v>8.270253259413295</v>
+        <v>8.229401125128481</v>
       </c>
       <c r="N15" t="n">
-        <v>123.79051633194</v>
+        <v>122.9422429181964</v>
       </c>
       <c r="O15" t="n">
-        <v>11.12611865530563</v>
+        <v>11.08793231031811</v>
       </c>
       <c r="P15" t="n">
-        <v>359.4642017258873</v>
+        <v>359.4340735264632</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37036,7 +37292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P551"/>
+  <dimension ref="A1:P555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82161,6 +82417,334 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-40.78960252313344,172.210671976213</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-40.788969969231566,172.211001990773</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-40.78831544018836,172.21125893649375</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-40.78766160116844,172.21151819779465</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-40.78703127579122,172.2118099558862</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-40.78639272753793,172.2120495877945</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-40.7857536622864,172.21235020470195</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-40.78510523616409,172.21262267881005</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-40.784448199103515,172.21285537083992</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-40.78379190224759,172.21306971404783</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-40.78313435188874,172.21325722337653</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-40.782481370286284,172.21349740196476</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>-40.78183338204009,172.2137846088499</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>-40.781181959954964,172.2140520572622</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-40.78959602842555,172.2106503748212</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-40.788967914796885,172.21099515773668</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-40.78831010530797,172.21124119280324</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-40.78765855267926,172.21150805863437</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-40.78702749760239,172.21179574877038</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-40.78638663666325,172.2120224197505</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-40.78574560018105,172.21231293024178</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-40.785100699726215,172.2126017049903</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-40.78444275048111,172.21283017969324</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-40.78378848402641,172.21305288335768</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-40.78313345128646,172.21325226710493</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-40.78247924595517,172.21348515486739</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>-40.781828652449335,172.21375734197608</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>-40.78117666928092,172.21402155561594</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-40.789591753845194,172.21063615758098</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-40.78896847810965,172.2109970313111</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-40.7883089124151,172.21123722527034</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-40.78766037514572,172.21151412008876</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-40.78702770584907,172.21179653183972</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-40.7863866111784,172.21202230607668</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-40.78574463864474,172.21230848466456</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-40.7851006504171,172.21260147701403</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-40.784443292878166,172.21283268740902</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-40.78378941415486,172.21305746313712</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-40.783133681673114,172.21325353498835</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>-40.7824784844022,172.2134807643987</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>-40.781828111351665,172.21375422246112</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>-40.78117875348681,172.2140335714154</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-40.78958655144662,172.21061885443063</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-40.788967086395694,172.21099240248023</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-40.7883091443665,172.21123799673506</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-40.78766011005971,172.21151323842264</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-40.787026129124115,172.2117906028863</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-40.78638561726937,172.21201787279801</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-40.78574382503699,172.2123047230224</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-40.78509983681642,172.21259771540537</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-40.78444181361336,172.21282584818428</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-40.78378787944281,172.21304990650108</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-40.783132864847666,172.21324903976532</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>-40.782477201786264,172.21347336992537</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>-40.781826908912116,172.2137472902058</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>-40.78117767130313,172.2140273324425</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P555"/>
+  <dimension ref="A1:P557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30394,6 +30394,114 @@
         <v>368.51</v>
       </c>
       <c r="P555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="C556" t="n">
+        <v>373.34</v>
+      </c>
+      <c r="D556" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="E556" t="n">
+        <v>384.54</v>
+      </c>
+      <c r="F556" t="n">
+        <v>388.96</v>
+      </c>
+      <c r="G556" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="H556" t="n">
+        <v>386.75</v>
+      </c>
+      <c r="I556" t="n">
+        <v>383.48</v>
+      </c>
+      <c r="J556" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="K556" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="L556" t="n">
+        <v>387</v>
+      </c>
+      <c r="M556" t="n">
+        <v>385.16</v>
+      </c>
+      <c r="N556" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="O556" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="C557" t="n">
+        <v>371.62</v>
+      </c>
+      <c r="D557" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="E557" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="F557" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="G557" t="n">
+        <v>391.14</v>
+      </c>
+      <c r="H557" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="I557" t="n">
+        <v>385.27</v>
+      </c>
+      <c r="J557" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="K557" t="n">
+        <v>385.78</v>
+      </c>
+      <c r="L557" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="M557" t="n">
+        <v>385.26</v>
+      </c>
+      <c r="N557" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="O557" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="P557" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30410,7 +30518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B563"/>
+  <dimension ref="A1:B565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36043,6 +36151,26 @@
       </c>
       <c r="B563" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>-0.95</v>
       </c>
     </row>
   </sheetData>
@@ -36211,28 +36339,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.151311434544089</v>
+        <v>-0.1574041362073317</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0146802418652765</v>
+        <v>0.0159198023393039</v>
       </c>
       <c r="M2" t="n">
-        <v>7.929601320138639</v>
+        <v>7.937975974168062</v>
       </c>
       <c r="N2" t="n">
-        <v>94.3243350533846</v>
+        <v>94.31657812195034</v>
       </c>
       <c r="O2" t="n">
-        <v>9.712071614922564</v>
+        <v>9.711672261868722</v>
       </c>
       <c r="P2" t="n">
-        <v>391.8946768579619</v>
+        <v>391.9568800289189</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36293,28 +36421,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.555008828900721</v>
+        <v>0.5584285945423519</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1415750310319698</v>
+        <v>0.143805896407888</v>
       </c>
       <c r="M3" t="n">
-        <v>8.568863059710585</v>
+        <v>8.557673869342223</v>
       </c>
       <c r="N3" t="n">
-        <v>114.6441064478637</v>
+        <v>114.3388367071517</v>
       </c>
       <c r="O3" t="n">
-        <v>10.7071988142494</v>
+        <v>10.69293396160061</v>
       </c>
       <c r="P3" t="n">
-        <v>352.2332614026755</v>
+        <v>352.1983563943038</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36375,28 +36503,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7546963224105661</v>
+        <v>0.7580386477821393</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2122390647804728</v>
+        <v>0.2147495085495992</v>
       </c>
       <c r="M4" t="n">
-        <v>8.836316198919818</v>
+        <v>8.819538548342527</v>
       </c>
       <c r="N4" t="n">
-        <v>129.7626956290239</v>
+        <v>129.3962434167386</v>
       </c>
       <c r="O4" t="n">
-        <v>11.39134301252596</v>
+        <v>11.37524696069227</v>
       </c>
       <c r="P4" t="n">
-        <v>353.7466176614149</v>
+        <v>353.7124972654175</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36453,28 +36581,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8737269265075616</v>
+        <v>0.8814626348379094</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2923684197090137</v>
+        <v>0.2964839005906197</v>
       </c>
       <c r="M5" t="n">
-        <v>8.394036473589559</v>
+        <v>8.399295434859841</v>
       </c>
       <c r="N5" t="n">
-        <v>113.4134235011124</v>
+        <v>113.5386360872319</v>
       </c>
       <c r="O5" t="n">
-        <v>10.64957386476625</v>
+        <v>10.65545100346446</v>
       </c>
       <c r="P5" t="n">
-        <v>348.931998595934</v>
+        <v>348.8530141845014</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36531,28 +36659,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8218813101043715</v>
+        <v>0.829774527430539</v>
       </c>
       <c r="J6" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K6" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2877951379044503</v>
+        <v>0.2920322005598819</v>
       </c>
       <c r="M6" t="n">
-        <v>8.080337057196125</v>
+        <v>8.084998824554352</v>
       </c>
       <c r="N6" t="n">
-        <v>102.6067578035359</v>
+        <v>102.7935571266901</v>
       </c>
       <c r="O6" t="n">
-        <v>10.12949938563283</v>
+        <v>10.1387157533235</v>
       </c>
       <c r="P6" t="n">
-        <v>355.075928465434</v>
+        <v>354.99532750732</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36609,28 +36737,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7275415021911693</v>
+        <v>0.7370969099533731</v>
       </c>
       <c r="J7" t="n">
+        <v>556</v>
+      </c>
+      <c r="K7" t="n">
         <v>554</v>
       </c>
-      <c r="K7" t="n">
-        <v>552</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2207746640080345</v>
+        <v>0.2252695326121112</v>
       </c>
       <c r="M7" t="n">
-        <v>8.92841569077815</v>
+        <v>8.94108712227027</v>
       </c>
       <c r="N7" t="n">
-        <v>113.505251465844</v>
+        <v>113.8979252866332</v>
       </c>
       <c r="O7" t="n">
-        <v>10.65388433698451</v>
+        <v>10.67229709512592</v>
       </c>
       <c r="P7" t="n">
-        <v>356.3915459523571</v>
+        <v>356.2931712405708</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36687,28 +36815,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.620369621453235</v>
+        <v>0.6303558816808691</v>
       </c>
       <c r="J8" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K8" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L8" t="n">
-        <v>0.214122995399778</v>
+        <v>0.2189697269802215</v>
       </c>
       <c r="M8" t="n">
-        <v>7.527254037028058</v>
+        <v>7.556086790025422</v>
       </c>
       <c r="N8" t="n">
-        <v>86.70189525258813</v>
+        <v>87.28072462713435</v>
       </c>
       <c r="O8" t="n">
-        <v>9.311385248854659</v>
+        <v>9.342415352955271</v>
       </c>
       <c r="P8" t="n">
-        <v>355.2490251569812</v>
+        <v>355.1470486689894</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36765,28 +36893,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8660136333546711</v>
+        <v>0.8747561434140645</v>
       </c>
       <c r="J9" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K9" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4200729180161195</v>
+        <v>0.4240355097066492</v>
       </c>
       <c r="M9" t="n">
-        <v>6.209452517529593</v>
+        <v>6.240356259728792</v>
       </c>
       <c r="N9" t="n">
-        <v>63.55276334682964</v>
+        <v>64.00743412177565</v>
       </c>
       <c r="O9" t="n">
-        <v>7.971998704642998</v>
+        <v>8.000464619119045</v>
       </c>
       <c r="P9" t="n">
-        <v>347.4030946997963</v>
+        <v>347.3138173590191</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36843,28 +36971,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.670456270475038</v>
+        <v>0.6794973939122333</v>
       </c>
       <c r="J10" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K10" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3096618493690457</v>
+        <v>0.3143583498063444</v>
       </c>
       <c r="M10" t="n">
-        <v>6.210058190344669</v>
+        <v>6.245128354318457</v>
       </c>
       <c r="N10" t="n">
-        <v>61.23199687696233</v>
+        <v>61.73611525240837</v>
       </c>
       <c r="O10" t="n">
-        <v>7.825087659378797</v>
+        <v>7.857233307749515</v>
       </c>
       <c r="P10" t="n">
-        <v>352.4627807844812</v>
+        <v>352.3701120122777</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36921,28 +37049,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6423751993123155</v>
+        <v>0.6502666242634337</v>
       </c>
       <c r="J11" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K11" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2627843497654964</v>
+        <v>0.267366945010064</v>
       </c>
       <c r="M11" t="n">
-        <v>7.075139677930507</v>
+        <v>7.101417046158776</v>
       </c>
       <c r="N11" t="n">
-        <v>70.73525400402451</v>
+        <v>71.03186855471752</v>
       </c>
       <c r="O11" t="n">
-        <v>8.410425316476243</v>
+        <v>8.428040611833662</v>
       </c>
       <c r="P11" t="n">
-        <v>356.0299468596217</v>
+        <v>355.9490671653306</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36999,28 +37127,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8562159206889137</v>
+        <v>0.863776531448226</v>
       </c>
       <c r="J12" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K12" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2458357410144756</v>
+        <v>0.2497049245376892</v>
       </c>
       <c r="M12" t="n">
-        <v>9.441641756278527</v>
+        <v>9.452470892146991</v>
       </c>
       <c r="N12" t="n">
-        <v>137.8966942768377</v>
+        <v>137.9067308225413</v>
       </c>
       <c r="O12" t="n">
-        <v>11.74294231770035</v>
+        <v>11.74336965366165</v>
       </c>
       <c r="P12" t="n">
-        <v>351.9981732681795</v>
+        <v>351.9207445312944</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37077,28 +37205,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5751240289939457</v>
+        <v>0.5841886637227246</v>
       </c>
       <c r="J13" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K13" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09974513136167817</v>
+        <v>0.1028538071857629</v>
       </c>
       <c r="M13" t="n">
-        <v>9.562730327822774</v>
+        <v>9.582227718212142</v>
       </c>
       <c r="N13" t="n">
-        <v>183.0472177648042</v>
+        <v>183.1162015804408</v>
       </c>
       <c r="O13" t="n">
-        <v>13.52949436471312</v>
+        <v>13.53204351088337</v>
       </c>
       <c r="P13" t="n">
-        <v>355.5498163827299</v>
+        <v>355.4569804714728</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37155,28 +37283,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4493333988356901</v>
+        <v>0.454629877176933</v>
       </c>
       <c r="J14" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K14" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07263386616064171</v>
+        <v>0.07459330393761687</v>
       </c>
       <c r="M14" t="n">
-        <v>9.555298988065291</v>
+        <v>9.550339520898047</v>
       </c>
       <c r="N14" t="n">
-        <v>157.8379262572626</v>
+        <v>157.517025462052</v>
       </c>
       <c r="O14" t="n">
-        <v>12.56335648850508</v>
+        <v>12.55057869032548</v>
       </c>
       <c r="P14" t="n">
-        <v>355.1871208613578</v>
+        <v>355.1328580671093</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37233,28 +37361,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2344684612811009</v>
+        <v>0.236259219312846</v>
       </c>
       <c r="J15" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K15" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02671433308730775</v>
+        <v>0.02728895645204998</v>
       </c>
       <c r="M15" t="n">
-        <v>8.229401125128481</v>
+        <v>8.211093695700386</v>
       </c>
       <c r="N15" t="n">
-        <v>122.9422429181964</v>
+        <v>122.5285745108497</v>
       </c>
       <c r="O15" t="n">
-        <v>11.08793231031811</v>
+        <v>11.06926260013962</v>
       </c>
       <c r="P15" t="n">
-        <v>359.4340735264632</v>
+        <v>359.4157888895159</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37292,7 +37420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P555"/>
+  <dimension ref="A1:P557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82745,6 +82873,170 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-40.789584496995516,172.21061202134015</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-40.78896539645705,172.21098678175724</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-40.788310768026186,172.21124339698824</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-40.78766064023172,172.2115150017549</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-40.78702487964377,172.21178590447062</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-40.786385872117854,172.2120190095361</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-40.78574313470301,172.21230153132612</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-40.785095966047884,172.21257981926846</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-40.784439323516715,172.21281433549004</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-40.783785321588304,172.21303731210847</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-40.78312940904572,172.21323002151536</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-40.78247231180874,172.21344517849852</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-40.781826908912116,172.2137472902058</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>-40.78117767130313,172.2140273324425</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-40.78958161413602,172.210602432972</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-40.788971095856866,172.21100573792216</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-40.78831351830631,172.21125254435648</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-40.787660772774736,172.21151544258797</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-40.78702151794567,172.21177326349593</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-40.78638424108736,172.2120117344124</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-40.785738820113764,172.21228158322583</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-40.78509155287531,172.21255941539522</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-40.78443648825676,172.21280122697783</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-40.78378462399139,172.21303387727428</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-40.78313024681618,172.21323463200002</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-40.78247211139967,172.21344402311226</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-40.781828251636256,172.21375503122425</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>-40.78117759114138,172.21402687029638</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0322/nzd0322.xlsx
+++ b/data/nzd0322/nzd0322.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P557"/>
+  <dimension ref="A1:P562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30493,7 +30493,7 @@
         <v>386.6</v>
       </c>
       <c r="M557" t="n">
-        <v>385.26</v>
+        <v>385</v>
       </c>
       <c r="N557" t="n">
         <v>375.21</v>
@@ -30502,6 +30502,276 @@
         <v>368.55</v>
       </c>
       <c r="P557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>379.31</v>
+      </c>
+      <c r="C558" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="D558" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="E558" t="n">
+        <v>383.88</v>
+      </c>
+      <c r="F558" t="n">
+        <v>389.53</v>
+      </c>
+      <c r="G558" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="H558" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="I558" t="n">
+        <v>385.29</v>
+      </c>
+      <c r="J558" t="n">
+        <v>385.55</v>
+      </c>
+      <c r="K558" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="L558" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="M558" t="n">
+        <v>384.86</v>
+      </c>
+      <c r="N558" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="O558" t="n">
+        <v>368.3</v>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>379.74</v>
+      </c>
+      <c r="C559" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="D559" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="E559" t="n">
+        <v>383.53</v>
+      </c>
+      <c r="F559" t="n">
+        <v>389.15</v>
+      </c>
+      <c r="G559" t="n">
+        <v>391.72</v>
+      </c>
+      <c r="H559" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="I559" t="n">
+        <v>386.19</v>
+      </c>
+      <c r="J559" t="n">
+        <v>386.96</v>
+      </c>
+      <c r="K559" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="L559" t="n">
+        <v>386.82</v>
+      </c>
+      <c r="M559" t="n">
+        <v>384.91</v>
+      </c>
+      <c r="N559" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="O559" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>380.13</v>
+      </c>
+      <c r="C560" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="D560" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="E560" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="F560" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="G560" t="n">
+        <v>391.04</v>
+      </c>
+      <c r="H560" t="n">
+        <v>387.88</v>
+      </c>
+      <c r="I560" t="n">
+        <v>386.07</v>
+      </c>
+      <c r="J560" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="K560" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="L560" t="n">
+        <v>386.02</v>
+      </c>
+      <c r="M560" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="N560" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="O560" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="C561" t="n">
+        <v>369</v>
+      </c>
+      <c r="D561" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="E561" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="F561" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="G561" t="n">
+        <v>390.81</v>
+      </c>
+      <c r="H561" t="n">
+        <v>388.03</v>
+      </c>
+      <c r="I561" t="n">
+        <v>386.32</v>
+      </c>
+      <c r="J561" t="n">
+        <v>386.64</v>
+      </c>
+      <c r="K561" t="n">
+        <v>386.41</v>
+      </c>
+      <c r="L561" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="M561" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="N561" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="O561" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="C562" t="n">
+        <v>367.69</v>
+      </c>
+      <c r="D562" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="E562" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="F562" t="n">
+        <v>387.84</v>
+      </c>
+      <c r="G562" t="n">
+        <v>389.81</v>
+      </c>
+      <c r="H562" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="I562" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="J562" t="n">
+        <v>386.18</v>
+      </c>
+      <c r="K562" t="n">
+        <v>385.68</v>
+      </c>
+      <c r="L562" t="n">
+        <v>385.71</v>
+      </c>
+      <c r="M562" t="n">
+        <v>383</v>
+      </c>
+      <c r="N562" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="O562" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="P562" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30518,7 +30788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B565"/>
+  <dimension ref="A1:B570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36171,6 +36441,56 @@
       </c>
       <c r="B565" t="n">
         <v>-0.95</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -36339,28 +36659,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1574041362073317</v>
+        <v>-0.1680758525013461</v>
       </c>
       <c r="J2" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0159198023393039</v>
+        <v>0.01833508238673209</v>
       </c>
       <c r="M2" t="n">
-        <v>7.937975974168062</v>
+        <v>7.930946412977786</v>
       </c>
       <c r="N2" t="n">
-        <v>94.31657812195034</v>
+        <v>93.90497803292079</v>
       </c>
       <c r="O2" t="n">
-        <v>9.711672261868722</v>
+        <v>9.690458092005805</v>
       </c>
       <c r="P2" t="n">
-        <v>391.9568800289189</v>
+        <v>392.0663261041808</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36421,28 +36741,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5584285945423519</v>
+        <v>0.5613782551427979</v>
       </c>
       <c r="J3" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K3" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.143805896407888</v>
+        <v>0.1471992957571786</v>
       </c>
       <c r="M3" t="n">
-        <v>8.557673869342223</v>
+        <v>8.498040853721843</v>
       </c>
       <c r="N3" t="n">
-        <v>114.3388367071517</v>
+        <v>113.3575773949612</v>
       </c>
       <c r="O3" t="n">
-        <v>10.69293396160061</v>
+        <v>10.64695155408163</v>
       </c>
       <c r="P3" t="n">
-        <v>352.1983563943038</v>
+        <v>352.1681122583926</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36503,28 +36823,28 @@
         <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7580386477821393</v>
+        <v>0.7632172990717385</v>
       </c>
       <c r="J4" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2147495085495992</v>
+        <v>0.2198372145202825</v>
       </c>
       <c r="M4" t="n">
-        <v>8.819538548342527</v>
+        <v>8.76374933308716</v>
       </c>
       <c r="N4" t="n">
-        <v>129.3962434167386</v>
+        <v>128.3447161267231</v>
       </c>
       <c r="O4" t="n">
-        <v>11.37524696069227</v>
+        <v>11.32893270024688</v>
       </c>
       <c r="P4" t="n">
-        <v>353.7124972654175</v>
+        <v>353.6593857564089</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36581,28 +36901,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8814626348379094</v>
+        <v>0.8977511071224961</v>
       </c>
       <c r="J5" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2964839005906197</v>
+        <v>0.3060009586793223</v>
       </c>
       <c r="M5" t="n">
-        <v>8.399295434859841</v>
+        <v>8.398080469531905</v>
       </c>
       <c r="N5" t="n">
-        <v>113.5386360872319</v>
+        <v>113.4868514707141</v>
       </c>
       <c r="O5" t="n">
-        <v>10.65545100346446</v>
+        <v>10.65302076740274</v>
       </c>
       <c r="P5" t="n">
-        <v>348.8530141845014</v>
+        <v>348.6859328549492</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36659,28 +36979,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.829774527430539</v>
+        <v>0.847677352066861</v>
       </c>
       <c r="J6" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K6" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2920322005598819</v>
+        <v>0.3021561806398123</v>
       </c>
       <c r="M6" t="n">
-        <v>8.084998824554352</v>
+        <v>8.089454599270098</v>
       </c>
       <c r="N6" t="n">
-        <v>102.7935571266901</v>
+        <v>103.0351669875754</v>
       </c>
       <c r="O6" t="n">
-        <v>10.1387157533235</v>
+        <v>10.15062397035647</v>
       </c>
       <c r="P6" t="n">
-        <v>354.99532750732</v>
+        <v>354.8116828167393</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36737,28 +37057,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7370969099533731</v>
+        <v>0.7602310456699863</v>
       </c>
       <c r="J7" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K7" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2252695326121112</v>
+        <v>0.2363147263418427</v>
       </c>
       <c r="M7" t="n">
-        <v>8.94108712227027</v>
+        <v>8.968735965778009</v>
       </c>
       <c r="N7" t="n">
-        <v>113.8979252866332</v>
+        <v>114.7838839835419</v>
       </c>
       <c r="O7" t="n">
-        <v>10.67229709512592</v>
+        <v>10.71372409498872</v>
       </c>
       <c r="P7" t="n">
-        <v>356.2931712405708</v>
+        <v>356.0539055899861</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36815,28 +37135,28 @@
         <v>0.0559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6303558816808691</v>
+        <v>0.6551015652828555</v>
       </c>
       <c r="J8" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K8" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2189697269802215</v>
+        <v>0.2309827184308438</v>
       </c>
       <c r="M8" t="n">
-        <v>7.556086790025422</v>
+        <v>7.630491978163534</v>
       </c>
       <c r="N8" t="n">
-        <v>87.28072462713435</v>
+        <v>88.70976946503914</v>
       </c>
       <c r="O8" t="n">
-        <v>9.342415352955271</v>
+        <v>9.418586383584277</v>
       </c>
       <c r="P8" t="n">
-        <v>355.1470486689894</v>
+        <v>354.8931980578357</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36893,28 +37213,28 @@
         <v>0.1309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8747561434140645</v>
+        <v>0.8983197695651519</v>
       </c>
       <c r="J9" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K9" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4240355097066492</v>
+        <v>0.4336370574464724</v>
       </c>
       <c r="M9" t="n">
-        <v>6.240356259728792</v>
+        <v>6.327921972785289</v>
       </c>
       <c r="N9" t="n">
-        <v>64.00743412177565</v>
+        <v>65.43768407637315</v>
       </c>
       <c r="O9" t="n">
-        <v>8.000464619119045</v>
+        <v>8.089356221379619</v>
       </c>
       <c r="P9" t="n">
-        <v>347.3138173590191</v>
+        <v>347.0720830687171</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36971,28 +37291,28 @@
         <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6794973939122333</v>
+        <v>0.704118445870607</v>
       </c>
       <c r="J10" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K10" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3143583498063444</v>
+        <v>0.325984092091542</v>
       </c>
       <c r="M10" t="n">
-        <v>6.245128354318457</v>
+        <v>6.344937642252024</v>
       </c>
       <c r="N10" t="n">
-        <v>61.73611525240837</v>
+        <v>63.35707886411432</v>
       </c>
       <c r="O10" t="n">
-        <v>7.857233307749515</v>
+        <v>7.959716003986218</v>
       </c>
       <c r="P10" t="n">
-        <v>352.3701120122777</v>
+        <v>352.1165850855526</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37049,28 +37369,28 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6502666242634337</v>
+        <v>0.6702430212780576</v>
       </c>
       <c r="J11" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K11" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="L11" t="n">
-        <v>0.267366945010064</v>
+        <v>0.2787846223951289</v>
       </c>
       <c r="M11" t="n">
-        <v>7.101417046158776</v>
+        <v>7.168177341646194</v>
       </c>
       <c r="N11" t="n">
-        <v>71.03186855471752</v>
+        <v>71.82749611600079</v>
       </c>
       <c r="O11" t="n">
-        <v>8.428040611833662</v>
+        <v>8.4751103896056</v>
       </c>
       <c r="P11" t="n">
-        <v>355.9490671653306</v>
+        <v>355.7433725925223</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37127,28 +37447,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.863776531448226</v>
+        <v>0.8811605231634915</v>
       </c>
       <c r="J12" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K12" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2497049245376892</v>
+        <v>0.2589928378204317</v>
       </c>
       <c r="M12" t="n">
-        <v>9.452470892146991</v>
+        <v>9.469700020234356</v>
       </c>
       <c r="N12" t="n">
-        <v>137.9067308225413</v>
+        <v>137.7587541346003</v>
       </c>
       <c r="O12" t="n">
-        <v>11.74336965366165</v>
+        <v>11.73706752705293</v>
       </c>
       <c r="P12" t="n">
-        <v>351.9207445312944</v>
+        <v>351.7418673417516</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37205,28 +37525,28 @@
         <v>0.0624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5841886637227246</v>
+        <v>0.6043845721970883</v>
       </c>
       <c r="J13" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K13" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1028538071857629</v>
+        <v>0.1101751699824609</v>
       </c>
       <c r="M13" t="n">
-        <v>9.582227718212142</v>
+        <v>9.617355555767229</v>
       </c>
       <c r="N13" t="n">
-        <v>183.1162015804408</v>
+        <v>182.9456222219866</v>
       </c>
       <c r="O13" t="n">
-        <v>13.53204351088337</v>
+        <v>13.52573924863209</v>
       </c>
       <c r="P13" t="n">
-        <v>355.4569804714728</v>
+        <v>355.2491760601849</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37283,28 +37603,28 @@
         <v>0.0541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.454629877176933</v>
+        <v>0.4667815461513803</v>
       </c>
       <c r="J14" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K14" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07459330393761687</v>
+        <v>0.07931029714104743</v>
       </c>
       <c r="M14" t="n">
-        <v>9.550339520898047</v>
+        <v>9.532225092993455</v>
       </c>
       <c r="N14" t="n">
-        <v>157.517025462052</v>
+        <v>156.6391537393323</v>
       </c>
       <c r="O14" t="n">
-        <v>12.55057869032548</v>
+        <v>12.51555646942366</v>
       </c>
       <c r="P14" t="n">
-        <v>355.1328580671093</v>
+        <v>355.0077680516052</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37361,28 +37681,28 @@
         <v>0.0557</v>
       </c>
       <c r="I15" t="n">
-        <v>0.236259219312846</v>
+        <v>0.2402784448135868</v>
       </c>
       <c r="J15" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K15" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02728895645204998</v>
+        <v>0.02865731507859004</v>
       </c>
       <c r="M15" t="n">
-        <v>8.211093695700386</v>
+        <v>8.162955145768317</v>
       </c>
       <c r="N15" t="n">
-        <v>122.5285745108497</v>
+        <v>121.4966112970512</v>
       </c>
       <c r="O15" t="n">
-        <v>11.06926260013962</v>
+        <v>11.02255012676519</v>
       </c>
       <c r="P15" t="n">
-        <v>359.4157888895159</v>
+        <v>359.3745601318415</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37420,7 +37740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P557"/>
+  <dimension ref="A1:P562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83018,7 +83338,7 @@
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t>-40.78247211139967,172.21344402311226</t>
+          <t>-40.78247263246321,172.21344702711653</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -83032,6 +83352,416 @@
         </is>
       </c>
       <c r="P557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-40.78957942713865,172.2105951590381</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-40.78897735856588,172.2110265676653</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-40.788316202313915,172.2112614713069</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-40.787662827191006,172.21152227550067</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-40.78702318392012,172.21177952804956</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-40.78638518402692,172.21201594034326</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-40.7857398802703,172.2122864847588</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-40.78509150356611,172.21255918741898</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-40.784435625351264,172.21279723743086</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-40.783784228686415,172.21303193086828</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-40.78313085419965,172.21323797460147</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-40.78247291303585,172.21344864465732</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>-40.78182853220541,172.21375664875052</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>-40.78117809215238,172.21402975870973</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-40.78957800227647,172.2105904199602</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-40.78897609939717,172.2110223796743</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-40.788315307644794,172.2112584956567</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-40.78766398694196,172.2115261327903</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-40.78702431440258,172.2117837789969</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-40.78638276296559,172.21200514133184</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-40.785738696839736,172.21228101328015</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-40.785089284651136,172.21254892848938</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-40.78443214907347,172.21278116525698</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-40.78378253120001,172.2130235727722</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-40.78312978604245,172.21323209623344</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-40.78247281283135,172.2134480669642</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>-40.781827209522056,172.21374902326963</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>-40.78117703000896,172.2140236352735</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-40.78957670995945,172.21058612172695</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-40.78898034080695,172.21103648659198</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-40.788318554962004,172.2112692961653</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-40.78766597508614,172.21153274528712</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-40.78702559363256,172.21178858927956</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-40.7863844959359,172.21201287115045</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-40.78574034871149,172.2122886505525</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-40.78508958050652,172.21255029634662</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-40.784433036633956,172.2127852687906</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-40.78378341482315,172.21302792356187</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-40.783131461583004,172.21324131720297</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-40.782474836961924,172.21345973636596</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>-40.78182889293715,172.2137587284272</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>-40.78117857312288,172.21403253158658</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-40.7895699832811,172.2105637488745</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-40.788979777494816,172.2110346130169</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-40.78831865436966,172.21126962679315</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-40.78766733365112,172.21153726382684</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-40.78702580187928,172.21178937234885</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-40.786385082087506,172.21201548564804</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-40.7857399788895,172.21228694071536</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-40.78508896414111,172.21254744664404</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-40.78443293801613,172.21278481284241</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-40.78378315903751,172.21302666412274</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-40.783130791366865,172.2132376288151</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>-40.78247461651211,172.213458465441</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>-40.7818272896847,172.21374948541995</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>-40.78117696988762,172.21402328866392</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-40.78956736550857,172.21055504219916</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-40.78898411831111,172.2110490505671</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-40.78832233245219,172.21128186002363</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-40.787668957301726,172.21154266403312</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-40.78702821159096,172.21179843357953</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-40.7863876305721,172.2120268530293</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-40.785741532141685,172.21229412203144</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-40.78509009825339,172.21255269009683</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-40.78443407212103,172.2127900562466</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-40.7837848565237,172.213035022219</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-40.78313211085477,172.2132448903288</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-40.782476640641654,172.2134701348434</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-40.78183021561986,172.2137663539085</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-40.78117937474024,172.21403715304808</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
